--- a/diseases/d003/2010-2014.xlsx
+++ b/diseases/d003/2010-2014.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1895,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2345,9 +2336,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2777,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3233,9 +3218,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3659,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4121,9 +4100,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4541,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5009,9 +4982,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5453,9 +5423,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5897,9 +5864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6341,9 +6305,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6785,9 +6746,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7181,9 +7139,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7580,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8069,9 +8021,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8462,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8903,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9401,9 +9344,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9845,9 +9785,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10289,9 +10226,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10733,9 +10667,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11177,9 +11108,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11621,9 +11549,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12065,9 +11990,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12509,9 +12431,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12905,9 +12824,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13349,9 +13265,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13793,9 +13706,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14237,9 +14147,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14681,9 +14588,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15125,9 +15029,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15569,9 +15470,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16013,9 +15911,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16457,9 +16352,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -17345,9 +17237,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -18381,9 +18270,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -19565,9 +19451,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20601,9 +20484,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -20997,9 +20877,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -22181,9 +22058,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -23217,9 +23091,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -24253,9 +24124,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -25289,9 +25157,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -26473,9 +26338,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -27509,9 +27371,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -28545,9 +28404,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -29729,9 +29585,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -30765,9 +30618,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -31949,9 +31799,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -32985,9 +32832,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -34021,9 +33865,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -34417,9 +34258,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -35601,9 +35439,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -36637,9 +36472,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -37673,9 +37505,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -38709,9 +38538,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -39893,9 +39719,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -40929,9 +40752,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -42113,9 +41933,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -43149,9 +42966,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -44185,9 +43999,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -45369,9 +45180,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -46403,9 +46211,6 @@
         <v>0</v>
       </c>
       <c r="O307" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q307" t="n">
         <v>0</v>
       </c>
       <c r="R307" t="n">
